--- a/test_samples/DWIHARTA/sample3_ref.xlsx
+++ b/test_samples/DWIHARTA/sample3_ref.xlsx
@@ -516,7 +516,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>07.01.2025</t>
+          <t>07 Jan 2025</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -549,12 +549,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>25.12.2024</t>
+          <t>25 Dec 2024</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>20.12.2024</t>
+          <t>20 Dec 2024</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -596,7 +596,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>07.01.2025</t>
+          <t>07 Jan 2025</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -629,12 +629,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>25.12.2024</t>
+          <t>25 Dec 2024</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>20.12.2024</t>
+          <t>20 Dec 2024</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -676,7 +676,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>07.01.2025</t>
+          <t>07 Jan 2025</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -709,12 +709,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>25.12.2024</t>
+          <t>25 Dec 2024</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>20.12.2024</t>
+          <t>20 Dec 2024</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -756,7 +756,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07.01.2025</t>
+          <t>07 Jan 2025</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -789,12 +789,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>25.12.2024</t>
+          <t>25 Dec 2024</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>20.12.2024</t>
+          <t>20 Dec 2024</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -836,7 +836,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>07.01.2025</t>
+          <t>07 Jan 2025</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>25.12.2024</t>
+          <t>25 Dec 2024</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>20.12.2024</t>
+          <t>20 Dec 2024</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -916,7 +916,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>07.01.2025</t>
+          <t>07 Jan 2025</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>25.12.2024</t>
+          <t>25 Dec 2024</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>20.12.2024</t>
+          <t>20 Dec 2024</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
